--- a/docs/規格來源/第二階段-賠款月帳單/CLAIM_SUMMARY.xlsx
+++ b/docs/規格來源/第二階段-賠款月帳單/CLAIM_SUMMARY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/檔案位子範例/templet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF6FB85A-C8C6-4A99-8ADE-A3E255611E1A}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF067E8-0F87-484D-A920-129A0EDA5755}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="481" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-8370" windowWidth="16440" windowHeight="28320" tabRatio="481" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表2" sheetId="2" r:id="rId1"/>
@@ -151,10 +151,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(4) = (2) + (3)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>查成分表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -171,7 +167,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(9)=(6)x5%</t>
+    <t>(9)=(6)x6%</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -276,6 +272,10 @@
   </si>
   <si>
     <t>共保賠款月帳單</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4) = (2) - (3)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -1215,20 +1215,20 @@
     </row>
     <row r="3" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="2"/>
       <c r="E3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1290,30 +1290,30 @@
         <v>14</v>
       </c>
       <c r="D6" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="F6" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="G6" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="H6" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="I6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="33" t="s">
         <v>20</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="18"/>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="9" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="18"/>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="18"/>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="11" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="18"/>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="12" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="18"/>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="13" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="18"/>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="18"/>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="18"/>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="16" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="18"/>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="18"/>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="18" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="18"/>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="19" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="18"/>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="20" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="18"/>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="21" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="18"/>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="22" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="18"/>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="22"/>
@@ -1566,20 +1566,20 @@
     <row r="25" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
       <c r="B25" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
